--- a/nr-correct-bugs/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-correct-bugs/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-29T08:27:17+00:00</t>
+    <t>2024-02-29T08:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3433,13 +3433,13 @@
     <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
+    <t>[Donnée restreinte] : Date à partir de laquelle le professionnel exerce cette profession (dateEffetExercice).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
+  </si>
+  <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.issuer</t>
